--- a/配置表格/L灵植表.xlsx
+++ b/配置表格/L灵植表.xlsx
@@ -12,6 +12,7 @@
     <sheet name="说明" sheetId="3" r:id="rId3"/>
     <sheet name="编号表" sheetId="4" r:id="rId4"/>
     <sheet name="灵植数值表" sheetId="5" r:id="rId5"/>
+    <sheet name="完整性复核" sheetId="6" r:id="rIdConfig6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4161,7 +4162,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -4322,8 +4323,36 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4540,8 +4569,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -4758,8 +4809,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4908,8 +4973,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="18"/>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -5003,6 +5070,28 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="18" xfId="50"/>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="18" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="18" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="18" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="18" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="19" xfId="51"/>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -69232,4 +69321,89 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="45" t="str">
+        <x:v>检查项</x:v>
+      </x:c>
+      <x:c r="B1" s="45" t="str">
+        <x:v>记录数</x:v>
+      </x:c>
+      <x:c r="C1" s="45" t="str">
+        <x:v>处理</x:v>
+      </x:c>
+      <x:c r="D1" s="45" t="str">
+        <x:v>依据</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="43" t="str">
+        <x:v>君臣佐使及丹头</x:v>
+      </x:c>
+      <x:c r="B2" s="43" t="n">
+        <x:v>1176</x:v>
+      </x:c>
+      <x:c r="C2" s="43" t="str">
+        <x:v>正式药力/杂质/价格/容量/公式保持不变</x:v>
+      </x:c>
+      <x:c r="D2" s="43" t="str">
+        <x:v>L灵植说明及炼丹案v2.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="38" customHeight="1">
+      <x:c r="A3" s="43" t="str">
+        <x:v>同境同品质约束</x:v>
+      </x:c>
+      <x:c r="B3" s="43" t="str">
+        <x:v>7境×6品的材料基础</x:v>
+      </x:c>
+      <x:c r="C3" s="43" t="str">
+        <x:v>配方检索以ID；不可把物品ID与灵植ID混用</x:v>
+      </x:c>
+      <x:c r="D3" s="43" t="str">
+        <x:v>正式炼丹案§3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="38" customHeight="1">
+      <x:c r="A4" s="43" t="str">
+        <x:v>丹头容量</x:v>
+      </x:c>
+      <x:c r="B4" s="43" t="str">
+        <x:v>7/8/9份</x:v>
+      </x:c>
+      <x:c r="C4" s="43" t="str">
+        <x:v>不计入药力/药性/杂质；随炉消耗</x:v>
+      </x:c>
+      <x:c r="D4" s="43" t="str">
+        <x:v>正式炼丹案§1.2/6.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
+      <x:c r="A5" s="43" t="str">
+        <x:v>停用旧数值页</x:v>
+      </x:c>
+      <x:c r="B5" s="43" t="str">
+        <x:v>灵植数值表</x:v>
+      </x:c>
+      <x:c r="C5" s="43" t="str">
+        <x:v>保持停用，不复活历史机制</x:v>
+      </x:c>
+      <x:c r="D5" s="43" t="str">
+        <x:v>源表说明</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>